--- a/research/traditional_assets/database/data/germany/germany_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_precious_metals.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.511</v>
+        <v>3.6</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -606,37 +606,37 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.719</v>
+        <v>5.2</v>
       </c>
       <c r="V2">
-        <v>0.056171875</v>
+        <v>0.3851851851851852</v>
       </c>
       <c r="W2">
-        <v>-0.03961240310077519</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="X2">
-        <v>0.1040692272758935</v>
+        <v>0.08641999811087574</v>
       </c>
       <c r="Y2">
-        <v>-0.1436816303766687</v>
+        <v>0.2039025825342856</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.05829675153643547</v>
+        <v>0.3228699551569507</v>
       </c>
       <c r="AB2">
-        <v>0.1040692272758935</v>
+        <v>0.08641999811087574</v>
       </c>
       <c r="AC2">
-        <v>-0.1623659788123289</v>
+        <v>0.2364499570460749</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.719</v>
+        <v>-5.2</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0595149408161576</v>
+        <v>-0.6265060240963856</v>
       </c>
       <c r="AK2">
-        <v>-0.06669140153974584</v>
+        <v>-0.5591397849462365</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.511</v>
+        <v>3.6</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -695,7 +695,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -704,37 +704,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.719</v>
+        <v>5.2</v>
       </c>
       <c r="V3">
-        <v>0.056171875</v>
+        <v>0.3851851851851852</v>
       </c>
       <c r="W3">
-        <v>-0.03961240310077519</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="X3">
-        <v>0.1040692272758935</v>
+        <v>0.08641999811087574</v>
       </c>
       <c r="Y3">
-        <v>-0.1436816303766687</v>
+        <v>0.2039025825342856</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.05829675153643547</v>
+        <v>0.3228699551569507</v>
       </c>
       <c r="AB3">
-        <v>0.1040692272758935</v>
+        <v>0.08641999811087574</v>
       </c>
       <c r="AC3">
-        <v>-0.1623659788123289</v>
+        <v>0.2364499570460749</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.719</v>
+        <v>-5.2</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0595149408161576</v>
+        <v>-0.6265060240963856</v>
       </c>
       <c r="AK3">
-        <v>-0.06669140153974584</v>
+        <v>-0.5591397849462365</v>
       </c>
       <c r="AL3">
         <v>0</v>
